--- a/artfynd/A 2857-2025 artfynd.xlsx
+++ b/artfynd/A 2857-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>77734637</v>
+        <v>77734635</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Matrammen (öst om), Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592918.3918399712</v>
+        <v>592905</v>
       </c>
       <c r="R2" t="n">
-        <v>6698159.64118167</v>
+        <v>6698094</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,21 +743,11 @@
           <t>2019-05-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-05-08</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -784,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>gammal tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,12 +785,7 @@
         <v>77734636</v>
       </c>
       <c r="B3" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592918.3918399712</v>
+        <v>592918</v>
       </c>
       <c r="R3" t="n">
-        <v>6698159.64118167</v>
+        <v>6698160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,19 +855,9 @@
           <t>2019-05-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-05-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,6 +891,454 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>77734640</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Matrammen (öst om), Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>592916</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6698112</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-05-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-05-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>77734637</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Matrammen (öst om), Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>592918</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6698160</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-05-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-05-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>77734641</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Matrammen (öst om), Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>592916</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6698112</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-05-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-05-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>77734634</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6275</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101520</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Större flatbagge</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Peltis grossa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Matrammen (öst om), Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>592904</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6698083</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-05-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-05-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2857-2025 artfynd.xlsx
+++ b/artfynd/A 2857-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77734635</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77734636</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77734640</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77734637</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77734641</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,8 +1369,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77734634</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>